--- a/SCE_stdev_lt.xlsx
+++ b/SCE_stdev_lt.xlsx
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -148,13 +148,13 @@
         <v>4.5301918983459473</v>
       </c>
       <c r="C7" s="2">
-        <v>4.4024534225463867</v>
+        <v>4.4017295837402344</v>
       </c>
       <c r="D7" s="2">
         <v>5.3624835014343262</v>
       </c>
       <c r="E7" s="2">
-        <v>5.2307429313659668</v>
+        <v>5.2290501594543457</v>
       </c>
     </row>
     <row r="8">
@@ -165,13 +165,13 @@
         <v>5.0946636199951172</v>
       </c>
       <c r="C8" s="2">
-        <v>4.9111151695251465</v>
+        <v>4.8976635932922363</v>
       </c>
       <c r="D8" s="2">
         <v>5.4869284629821777</v>
       </c>
       <c r="E8" s="2">
-        <v>5.425262451171875</v>
+        <v>5.4241399765014648</v>
       </c>
     </row>
     <row r="9">
@@ -182,13 +182,13 @@
         <v>5.6854672431945801</v>
       </c>
       <c r="C9" s="2">
-        <v>5.6075968742370605</v>
+        <v>5.6096711158752441</v>
       </c>
       <c r="D9" s="2">
         <v>5.4606180191040039</v>
       </c>
       <c r="E9" s="2">
-        <v>5.3988656997680664</v>
+        <v>5.397885799407959</v>
       </c>
     </row>
     <row r="10">
@@ -199,13 +199,13 @@
         <v>5.9431967735290527</v>
       </c>
       <c r="C10" s="2">
-        <v>5.9193997383117676</v>
+        <v>5.915532112121582</v>
       </c>
       <c r="D10" s="2">
         <v>5.5678534507751465</v>
       </c>
       <c r="E10" s="2">
-        <v>5.5165834426879883</v>
+        <v>5.5159749984741211</v>
       </c>
     </row>
     <row r="11">
@@ -216,13 +216,13 @@
         <v>5.5588984489440918</v>
       </c>
       <c r="C11" s="2">
-        <v>5.3131504058837891</v>
+        <v>5.3206543922424316</v>
       </c>
       <c r="D11" s="2">
         <v>5.6390500068664551</v>
       </c>
       <c r="E11" s="2">
-        <v>5.5737957954406738</v>
+        <v>5.5733575820922852</v>
       </c>
     </row>
     <row r="12">
@@ -233,13 +233,13 @@
         <v>6.1091527938842773</v>
       </c>
       <c r="C12" s="2">
-        <v>6.3978590965270996</v>
+        <v>6.3995904922485352</v>
       </c>
       <c r="D12" s="2">
         <v>5.8802719116210938</v>
       </c>
       <c r="E12" s="2">
-        <v>5.8260383605957031</v>
+        <v>5.8258075714111328</v>
       </c>
     </row>
     <row r="13">
@@ -250,13 +250,13 @@
         <v>5.3027558326721191</v>
       </c>
       <c r="C13" s="2">
-        <v>5.2404861450195312</v>
+        <v>5.2403607368469238</v>
       </c>
       <c r="D13" s="2">
         <v>6.1278777122497559</v>
       </c>
       <c r="E13" s="2">
-        <v>6.1069808006286621</v>
+        <v>6.1094088554382324</v>
       </c>
     </row>
     <row r="14">
@@ -267,13 +267,13 @@
         <v>6.3185024261474609</v>
       </c>
       <c r="C14" s="2">
-        <v>6.3406047821044922</v>
+        <v>6.3425960540771484</v>
       </c>
       <c r="D14" s="2">
         <v>6.1767430305480957</v>
       </c>
       <c r="E14" s="2">
-        <v>6.1626725196838379</v>
+        <v>6.1642122268676758</v>
       </c>
     </row>
     <row r="15">
@@ -284,13 +284,13 @@
         <v>6.2086200714111328</v>
       </c>
       <c r="C15" s="2">
-        <v>6.031496524810791</v>
+        <v>6.0324182510375977</v>
       </c>
       <c r="D15" s="2">
         <v>6.1769070625305176</v>
       </c>
       <c r="E15" s="2">
-        <v>6.1685690879821777</v>
+        <v>6.1702055931091309</v>
       </c>
     </row>
     <row r="16">
@@ -301,13 +301,13 @@
         <v>6.7011919021606445</v>
       </c>
       <c r="C16" s="2">
-        <v>6.6726365089416504</v>
+        <v>6.6737809181213379</v>
       </c>
       <c r="D16" s="2">
         <v>6.1405487060546875</v>
       </c>
       <c r="E16" s="2">
-        <v>6.1645655632019043</v>
+        <v>6.1658549308776855</v>
       </c>
     </row>
     <row r="17">
@@ -318,13 +318,13 @@
         <v>7.323115348815918</v>
       </c>
       <c r="C17" s="2">
-        <v>7.4395976066589355</v>
+        <v>7.4500746726989746</v>
       </c>
       <c r="D17" s="2">
         <v>6.0390791893005371</v>
       </c>
       <c r="E17" s="2">
-        <v>6.0168967247009277</v>
+        <v>6.0184059143066406</v>
       </c>
     </row>
     <row r="18">
@@ -335,13 +335,13 @@
         <v>6.1252527236938477</v>
       </c>
       <c r="C18" s="2">
-        <v>6.108823299407959</v>
+        <v>6.1029019355773926</v>
       </c>
       <c r="D18" s="2">
         <v>5.976264476776123</v>
       </c>
       <c r="E18" s="2">
-        <v>5.9133305549621582</v>
+        <v>5.9148931503295898</v>
       </c>
     </row>
     <row r="19">
@@ -352,13 +352,13 @@
         <v>5.944674015045166</v>
       </c>
       <c r="C19" s="2">
-        <v>5.9724678993225098</v>
+        <v>5.9694714546203613</v>
       </c>
       <c r="D19" s="2">
         <v>5.8484854698181152</v>
       </c>
       <c r="E19" s="2">
-        <v>5.7804498672485352</v>
+        <v>5.7830467224121094</v>
       </c>
     </row>
     <row r="20">
@@ -369,13 +369,13 @@
         <v>5.2316741943359375</v>
       </c>
       <c r="C20" s="2">
-        <v>5.2771191596984863</v>
+        <v>5.281501293182373</v>
       </c>
       <c r="D20" s="2">
         <v>5.9609379768371582</v>
       </c>
       <c r="E20" s="2">
-        <v>5.906806468963623</v>
+        <v>5.9096298217773438</v>
       </c>
     </row>
     <row r="21">
@@ -386,13 +386,13 @@
         <v>5.1959242820739746</v>
       </c>
       <c r="C21" s="2">
-        <v>5.0688385963439941</v>
+        <v>5.0725483894348145</v>
       </c>
       <c r="D21" s="2">
         <v>5.8619036674499512</v>
       </c>
       <c r="E21" s="2">
-        <v>5.8037114143371582</v>
+        <v>5.8067355155944824</v>
       </c>
     </row>
     <row r="22">
@@ -403,13 +403,13 @@
         <v>4.7374272346496582</v>
       </c>
       <c r="C22" s="2">
-        <v>4.3083901405334473</v>
+        <v>4.3087449073791504</v>
       </c>
       <c r="D22" s="2">
         <v>5.6456847190856934</v>
       </c>
       <c r="E22" s="2">
-        <v>5.5467214584350586</v>
+        <v>5.5495696067810059</v>
       </c>
     </row>
     <row r="23">
@@ -420,13 +420,13 @@
         <v>5.1684908866882324</v>
       </c>
       <c r="C23" s="2">
-        <v>5.1446776390075684</v>
+        <v>5.155977725982666</v>
       </c>
       <c r="D23" s="2">
         <v>5.7407140731811523</v>
       </c>
       <c r="E23" s="2">
-        <v>5.6438984870910645</v>
+        <v>5.6478095054626465</v>
       </c>
     </row>
     <row r="24">
@@ -437,13 +437,13 @@
         <v>7.2206926345825195</v>
       </c>
       <c r="C24" s="2">
-        <v>7.1687092781066895</v>
+        <v>7.1716651916503906</v>
       </c>
       <c r="D24" s="2">
         <v>5.7031898498535156</v>
       </c>
       <c r="E24" s="2">
-        <v>5.5903353691101074</v>
+        <v>5.5956687927246094</v>
       </c>
     </row>
     <row r="25">
@@ -454,13 +454,13 @@
         <v>5.8098797798156738</v>
       </c>
       <c r="C25" s="2">
-        <v>5.7447772026062012</v>
+        <v>5.7477340698242188</v>
       </c>
       <c r="D25" s="2">
         <v>5.8179006576538086</v>
       </c>
       <c r="E25" s="2">
-        <v>5.7331933975219727</v>
+        <v>5.7368288040161133</v>
       </c>
     </row>
     <row r="26">
@@ -471,13 +471,13 @@
         <v>5.3771452903747559</v>
       </c>
       <c r="C26" s="2">
-        <v>5.1266913414001465</v>
+        <v>5.1355810165405273</v>
       </c>
       <c r="D26" s="2">
         <v>5.9916996955871582</v>
       </c>
       <c r="E26" s="2">
-        <v>5.918398380279541</v>
+        <v>5.9218029975891113</v>
       </c>
     </row>
     <row r="27">
@@ -488,13 +488,13 @@
         <v>6.9805169105529785</v>
       </c>
       <c r="C27" s="2">
-        <v>6.9834160804748535</v>
+        <v>6.9870615005493164</v>
       </c>
       <c r="D27" s="2">
         <v>6.1422090530395508</v>
       </c>
       <c r="E27" s="2">
-        <v>6.1192011833190918</v>
+        <v>6.1230711936950684</v>
       </c>
     </row>
     <row r="28">
@@ -505,13 +505,13 @@
         <v>5.606959342956543</v>
       </c>
       <c r="C28" s="2">
-        <v>5.4904007911682129</v>
+        <v>5.5002036094665527</v>
       </c>
       <c r="D28" s="2">
         <v>6.2517604827880859</v>
       </c>
       <c r="E28" s="2">
-        <v>6.225560188293457</v>
+        <v>6.2282090187072754</v>
       </c>
     </row>
     <row r="29">
@@ -522,13 +522,13 @@
         <v>6.2640681266784668</v>
       </c>
       <c r="C29" s="2">
-        <v>6.562840461730957</v>
+        <v>6.5519418716430664</v>
       </c>
       <c r="D29" s="2">
         <v>6.1346220970153809</v>
       </c>
       <c r="E29" s="2">
-        <v>6.105095386505127</v>
+        <v>6.1076517105102539</v>
       </c>
     </row>
     <row r="30">
@@ -539,13 +539,13 @@
         <v>6.7601170539855957</v>
       </c>
       <c r="C30" s="2">
-        <v>6.7356815338134766</v>
+        <v>6.7373166084289551</v>
       </c>
       <c r="D30" s="2">
         <v>6.103238582611084</v>
       </c>
       <c r="E30" s="2">
-        <v>6.0707693099975586</v>
+        <v>6.073944091796875</v>
       </c>
     </row>
     <row r="31">
@@ -556,13 +556,13 @@
         <v>6.0920100212097168</v>
       </c>
       <c r="C31" s="2">
-        <v>6.1156172752380371</v>
+        <v>6.1201591491699219</v>
       </c>
       <c r="D31" s="2">
         <v>6.1025605201721191</v>
       </c>
       <c r="E31" s="2">
-        <v>6.0982236862182617</v>
+        <v>6.1004300117492676</v>
       </c>
     </row>
     <row r="32">
@@ -573,13 +573,13 @@
         <v>6.1544570922851562</v>
       </c>
       <c r="C32" s="2">
-        <v>6.1019096374511719</v>
+        <v>6.1022176742553711</v>
       </c>
       <c r="D32" s="2">
         <v>5.9501290321350098</v>
       </c>
       <c r="E32" s="2">
-        <v>5.9490842819213867</v>
+        <v>5.9510602951049805</v>
       </c>
     </row>
     <row r="33">
@@ -590,13 +590,13 @@
         <v>6.1664457321166992</v>
       </c>
       <c r="C33" s="2">
-        <v>6.0845227241516113</v>
+        <v>6.0866508483886719</v>
       </c>
       <c r="D33" s="2">
         <v>5.8441224098205566</v>
       </c>
       <c r="E33" s="2">
-        <v>5.8491835594177246</v>
+        <v>5.8504900932312012</v>
       </c>
     </row>
     <row r="34">
@@ -607,13 +607,13 @@
         <v>5.5274257659912109</v>
       </c>
       <c r="C34" s="2">
-        <v>5.4358458518981934</v>
+        <v>5.444364070892334</v>
       </c>
       <c r="D34" s="2">
         <v>5.7594237327575684</v>
       </c>
       <c r="E34" s="2">
-        <v>5.7398648262023926</v>
+        <v>5.7417726516723633</v>
       </c>
     </row>
     <row r="35">
@@ -624,13 +624,13 @@
         <v>5.3710432052612305</v>
       </c>
       <c r="C35" s="2">
-        <v>5.3737783432006836</v>
+        <v>5.3739538192749023</v>
       </c>
       <c r="D35" s="2">
         <v>5.549527645111084</v>
       </c>
       <c r="E35" s="2">
-        <v>5.5110659599304199</v>
+        <v>5.5139918327331543</v>
       </c>
     </row>
     <row r="36">
@@ -641,13 +641,13 @@
         <v>5.6086359024047852</v>
       </c>
       <c r="C36" s="2">
-        <v>5.6411619186401367</v>
+        <v>5.6427345275878906</v>
       </c>
       <c r="D36" s="2">
         <v>5.6549420356750488</v>
       </c>
       <c r="E36" s="2">
-        <v>5.5776700973510742</v>
+        <v>5.581993579864502</v>
       </c>
     </row>
     <row r="37">
@@ -658,13 +658,13 @@
         <v>4.652897834777832</v>
       </c>
       <c r="C37" s="2">
-        <v>4.5912928581237793</v>
+        <v>4.5950717926025391</v>
       </c>
       <c r="D37" s="2">
         <v>5.640777587890625</v>
       </c>
       <c r="E37" s="2">
-        <v>5.5467114448547363</v>
+        <v>5.5509223937988281</v>
       </c>
     </row>
     <row r="38">
@@ -675,13 +675,13 @@
         <v>5.5017795562744141</v>
       </c>
       <c r="C38" s="2">
-        <v>5.5789752006530762</v>
+        <v>5.5734872817993164</v>
       </c>
       <c r="D38" s="2">
         <v>5.5401191711425781</v>
       </c>
       <c r="E38" s="2">
-        <v>5.4375548362731934</v>
+        <v>5.4415898323059082</v>
       </c>
     </row>
     <row r="39">
@@ -692,13 +692,13 @@
         <v>4.8710522651672363</v>
       </c>
       <c r="C39" s="2">
-        <v>4.6764898300170898</v>
+        <v>4.687286376953125</v>
       </c>
       <c r="D39" s="2">
         <v>5.5602965354919434</v>
       </c>
       <c r="E39" s="2">
-        <v>5.4551711082458496</v>
+        <v>5.459589958190918</v>
       </c>
     </row>
     <row r="40">
@@ -709,13 +709,13 @@
         <v>7.0407414436340332</v>
       </c>
       <c r="C40" s="2">
-        <v>6.7150564193725586</v>
+        <v>6.732177734375</v>
       </c>
       <c r="D40" s="2">
         <v>5.5558099746704102</v>
       </c>
       <c r="E40" s="2">
-        <v>5.4336004257202148</v>
+        <v>5.4384760856628418</v>
       </c>
     </row>
     <row r="41">
@@ -726,13 +726,13 @@
         <v>6.0269770622253418</v>
       </c>
       <c r="C41" s="2">
-        <v>5.8232812881469727</v>
+        <v>5.822573184967041</v>
       </c>
       <c r="D41" s="2">
         <v>5.6252870559692383</v>
       </c>
       <c r="E41" s="2">
-        <v>5.4879822731018066</v>
+        <v>5.4931368827819824</v>
       </c>
     </row>
     <row r="42">
@@ -743,13 +743,13 @@
         <v>5.260521411895752</v>
       </c>
       <c r="C42" s="2">
-        <v>5.1021113395690918</v>
+        <v>5.1026601791381836</v>
       </c>
       <c r="D42" s="2">
         <v>5.6961116790771484</v>
       </c>
       <c r="E42" s="2">
-        <v>5.5464425086975098</v>
+        <v>5.5515832901000977</v>
       </c>
     </row>
     <row r="43">
@@ -760,13 +760,13 @@
         <v>5.7090187072753906</v>
       </c>
       <c r="C43" s="2">
-        <v>5.5943927764892578</v>
+        <v>5.6063656806945801</v>
       </c>
       <c r="D43" s="2">
         <v>5.7380242347717285</v>
       </c>
       <c r="E43" s="2">
-        <v>5.574653148651123</v>
+        <v>5.5812745094299316</v>
       </c>
     </row>
     <row r="44">
@@ -777,13 +777,13 @@
         <v>5.3306670188903809</v>
       </c>
       <c r="C44" s="2">
-        <v>5.1796412467956543</v>
+        <v>5.1839299201965332</v>
       </c>
       <c r="D44" s="2">
         <v>5.889378547668457</v>
       </c>
       <c r="E44" s="2">
-        <v>5.7439241409301758</v>
+        <v>5.7493796348571777</v>
       </c>
     </row>
     <row r="45">
@@ -794,13 +794,13 @@
         <v>6.2339272499084473</v>
       </c>
       <c r="C45" s="2">
-        <v>6.1305985450744629</v>
+        <v>6.1346783638000488</v>
       </c>
       <c r="D45" s="2">
         <v>5.8384127616882324</v>
       </c>
       <c r="E45" s="2">
-        <v>5.7366476058959961</v>
+        <v>5.7395925521850586</v>
       </c>
     </row>
     <row r="46">
@@ -811,13 +811,13 @@
         <v>5.290318489074707</v>
       </c>
       <c r="C46" s="2">
-        <v>5.117434024810791</v>
+        <v>5.1210904121398926</v>
       </c>
       <c r="D46" s="2">
         <v>5.8637819290161133</v>
       </c>
       <c r="E46" s="2">
-        <v>5.7840566635131836</v>
+        <v>5.786963939666748</v>
       </c>
     </row>
     <row r="47">
@@ -828,13 +828,13 @@
         <v>5.8789925575256348</v>
       </c>
       <c r="C47" s="2">
-        <v>5.8328738212585449</v>
+        <v>5.8407068252563477</v>
       </c>
       <c r="D47" s="2">
         <v>6.0151686668395996</v>
       </c>
       <c r="E47" s="2">
-        <v>5.9625492095947266</v>
+        <v>5.9655356407165527</v>
       </c>
     </row>
     <row r="48">
@@ -845,13 +845,13 @@
         <v>6.2332439422607422</v>
       </c>
       <c r="C48" s="2">
-        <v>6.1999282836914062</v>
+        <v>6.2002358436584473</v>
       </c>
       <c r="D48" s="2">
         <v>6.1029829978942871</v>
       </c>
       <c r="E48" s="2">
-        <v>6.0703544616699219</v>
+        <v>6.0726847648620605</v>
       </c>
     </row>
     <row r="49">
@@ -862,13 +862,13 @@
         <v>6.5820488929748535</v>
       </c>
       <c r="C49" s="2">
-        <v>6.6495685577392578</v>
+        <v>6.6440935134887695</v>
       </c>
       <c r="D49" s="2">
         <v>6.2419490814208984</v>
       </c>
       <c r="E49" s="2">
-        <v>6.2282304763793945</v>
+        <v>6.2296404838562012</v>
       </c>
     </row>
     <row r="50">
@@ -879,13 +879,13 @@
         <v>6.2552971839904785</v>
       </c>
       <c r="C50" s="2">
-        <v>6.249962329864502</v>
+        <v>6.2489156723022461</v>
       </c>
       <c r="D50" s="2">
         <v>6.1711173057556152</v>
       </c>
       <c r="E50" s="2">
-        <v>6.1541128158569336</v>
+        <v>6.1541047096252441</v>
       </c>
     </row>
     <row r="51">
@@ -896,13 +896,13 @@
         <v>6.6230058670043945</v>
       </c>
       <c r="C51" s="2">
-        <v>6.7085433006286621</v>
+        <v>6.7098031044006348</v>
       </c>
       <c r="D51" s="2">
         <v>6.2361111640930176</v>
       </c>
       <c r="E51" s="2">
-        <v>6.2446403503417969</v>
+        <v>6.2451062202453613</v>
       </c>
     </row>
     <row r="52">
@@ -913,13 +913,13 @@
         <v>6.4993462562561035</v>
       </c>
       <c r="C52" s="2">
-        <v>6.5646414756774902</v>
+        <v>6.5707111358642578</v>
       </c>
       <c r="D52" s="2">
         <v>6.2097396850585938</v>
       </c>
       <c r="E52" s="2">
-        <v>6.218411922454834</v>
+        <v>6.2178454399108887</v>
       </c>
     </row>
     <row r="53">
@@ -930,13 +930,13 @@
         <v>6.5813608169555664</v>
       </c>
       <c r="C53" s="2">
-        <v>6.600522518157959</v>
+        <v>6.5965290069580078</v>
       </c>
       <c r="D53" s="2">
         <v>6.1219987869262695</v>
       </c>
       <c r="E53" s="2">
-        <v>6.1282405853271484</v>
+        <v>6.1279726028442383</v>
       </c>
     </row>
     <row r="54">
@@ -947,13 +947,13 @@
         <v>5.5964436531066895</v>
       </c>
       <c r="C54" s="2">
-        <v>5.4635415077209473</v>
+        <v>5.4548563957214355</v>
       </c>
       <c r="D54" s="2">
         <v>6.0554351806640625</v>
       </c>
       <c r="E54" s="2">
-        <v>6.0604691505432129</v>
+        <v>6.0603342056274414</v>
       </c>
     </row>
     <row r="55">
@@ -964,13 +964,13 @@
         <v>5.8752603530883789</v>
       </c>
       <c r="C55" s="2">
-        <v>5.9321813583374023</v>
+        <v>5.9401040077209473</v>
       </c>
       <c r="D55" s="2">
         <v>6.0392885208129883</v>
       </c>
       <c r="E55" s="2">
-        <v>6.0362644195556641</v>
+        <v>6.0357508659362793</v>
       </c>
     </row>
     <row r="56">
@@ -981,13 +981,13 @@
         <v>5.6416521072387695</v>
       </c>
       <c r="C56" s="2">
-        <v>5.5968184471130371</v>
+        <v>5.5953621864318848</v>
       </c>
       <c r="D56" s="2">
         <v>5.9759817123413086</v>
       </c>
       <c r="E56" s="2">
-        <v>5.9624218940734863</v>
+        <v>5.9617934226989746</v>
       </c>
     </row>
     <row r="57">
@@ -998,13 +998,13 @@
         <v>5.4435720443725586</v>
       </c>
       <c r="C57" s="2">
-        <v>5.3883862495422363</v>
+        <v>5.3913774490356445</v>
       </c>
       <c r="D57" s="2">
         <v>5.9282083511352539</v>
       </c>
       <c r="E57" s="2">
-        <v>5.9056916236877441</v>
+        <v>5.9038619995117188</v>
       </c>
     </row>
     <row r="58">
@@ -1015,13 +1015,13 @@
         <v>5.9829788208007812</v>
       </c>
       <c r="C58" s="2">
-        <v>6.0396242141723633</v>
+        <v>6.0353488922119141</v>
       </c>
       <c r="D58" s="2">
         <v>5.8540778160095215</v>
       </c>
       <c r="E58" s="2">
-        <v>5.8233718872070312</v>
+        <v>5.8216643333435059</v>
       </c>
     </row>
     <row r="59">
@@ -1032,13 +1032,13 @@
         <v>6.1099758148193359</v>
       </c>
       <c r="C59" s="2">
-        <v>6.0321226119995117</v>
+        <v>6.0276675224304199</v>
       </c>
       <c r="D59" s="2">
         <v>5.7844376564025879</v>
       </c>
       <c r="E59" s="2">
-        <v>5.778843879699707</v>
+        <v>5.7786717414855957</v>
       </c>
     </row>
     <row r="60">
@@ -1049,13 +1049,13 @@
         <v>6.0532450675964355</v>
       </c>
       <c r="C60" s="2">
-        <v>6.0439572334289551</v>
+        <v>6.0441832542419434</v>
       </c>
       <c r="D60" s="2">
         <v>5.7119460105895996</v>
       </c>
       <c r="E60" s="2">
-        <v>5.6851334571838379</v>
+        <v>5.6850810050964355</v>
       </c>
     </row>
     <row r="61">
@@ -1066,13 +1066,13 @@
         <v>6.0693883895874023</v>
       </c>
       <c r="C61" s="2">
-        <v>6.0540685653686523</v>
+        <v>6.0493302345275879</v>
       </c>
       <c r="D61" s="2">
         <v>5.862363338470459</v>
       </c>
       <c r="E61" s="2">
-        <v>5.8281970024108887</v>
+        <v>5.8275303840637207</v>
       </c>
     </row>
     <row r="62">
@@ -1083,13 +1083,13 @@
         <v>5.9141836166381836</v>
       </c>
       <c r="C62" s="2">
-        <v>5.8596482276916504</v>
+        <v>5.8567509651184082</v>
       </c>
       <c r="D62" s="2">
         <v>5.8301868438720703</v>
       </c>
       <c r="E62" s="2">
-        <v>5.7874112129211426</v>
+        <v>5.786221981048584</v>
       </c>
     </row>
     <row r="63">
@@ -1100,13 +1100,13 @@
         <v>4.9696807861328125</v>
       </c>
       <c r="C63" s="2">
-        <v>5.0627889633178711</v>
+        <v>5.0679192543029785</v>
       </c>
       <c r="D63" s="2">
         <v>5.844581127166748</v>
       </c>
       <c r="E63" s="2">
-        <v>5.7755002975463867</v>
+        <v>5.7754254341125488</v>
       </c>
     </row>
     <row r="64">
@@ -1117,13 +1117,13 @@
         <v>5.2228355407714844</v>
       </c>
       <c r="C64" s="2">
-        <v>5.0887856483459473</v>
+        <v>5.0977878570556641</v>
       </c>
       <c r="D64" s="2">
         <v>5.7785630226135254</v>
       </c>
       <c r="E64" s="2">
-        <v>5.7184247970581055</v>
+        <v>5.7192554473876953</v>
       </c>
     </row>
     <row r="65">
@@ -1134,13 +1134,13 @@
         <v>6.9954109191894531</v>
       </c>
       <c r="C65" s="2">
-        <v>6.8843932151794434</v>
+        <v>6.877406120300293</v>
       </c>
       <c r="D65" s="2">
         <v>5.6650252342224121</v>
       </c>
       <c r="E65" s="2">
-        <v>5.5911293029785156</v>
+        <v>5.5924139022827148</v>
       </c>
     </row>
     <row r="66">
@@ -1151,13 +1151,13 @@
         <v>5.1539840698242188</v>
       </c>
       <c r="C66" s="2">
-        <v>5.0213103294372559</v>
+        <v>5.0196042060852051</v>
       </c>
       <c r="D66" s="2">
         <v>5.7393555641174316</v>
       </c>
       <c r="E66" s="2">
-        <v>5.6490917205810547</v>
+        <v>5.6511721611022949</v>
       </c>
     </row>
     <row r="67">
@@ -1168,13 +1168,13 @@
         <v>6.1125249862670898</v>
       </c>
       <c r="C67" s="2">
-        <v>5.9324278831481934</v>
+        <v>5.9381780624389648</v>
       </c>
       <c r="D67" s="2">
         <v>5.6899991035461426</v>
       </c>
       <c r="E67" s="2">
-        <v>5.5971951484680176</v>
+        <v>5.5998940467834473</v>
       </c>
     </row>
     <row r="68">
@@ -1185,13 +1185,13 @@
         <v>5.5158147811889648</v>
       </c>
       <c r="C68" s="2">
-        <v>5.5184421539306641</v>
+        <v>5.5221409797668457</v>
       </c>
       <c r="D68" s="2">
         <v>5.6835708618164062</v>
       </c>
       <c r="E68" s="2">
-        <v>5.5668368339538574</v>
+        <v>5.56915283203125</v>
       </c>
     </row>
     <row r="69">
@@ -1202,13 +1202,13 @@
         <v>5.0314054489135742</v>
       </c>
       <c r="C69" s="2">
-        <v>4.8982973098754883</v>
+        <v>4.9026069641113281</v>
       </c>
       <c r="D69" s="2">
         <v>5.6933326721191406</v>
       </c>
       <c r="E69" s="2">
-        <v>5.5889148712158203</v>
+        <v>5.5894637107849121</v>
       </c>
     </row>
     <row r="70">
@@ -1219,13 +1219,13 @@
         <v>6.7383604049682617</v>
       </c>
       <c r="C70" s="2">
-        <v>6.5757331848144531</v>
+        <v>6.5781545639038086</v>
       </c>
       <c r="D70" s="2">
         <v>5.6192975044250488</v>
       </c>
       <c r="E70" s="2">
-        <v>5.5303363800048828</v>
+        <v>5.5301322937011719</v>
       </c>
     </row>
     <row r="71">
@@ -1236,13 +1236,13 @@
         <v>5.4699769020080566</v>
       </c>
       <c r="C71" s="2">
-        <v>5.3925786018371582</v>
+        <v>5.3952469825744629</v>
       </c>
       <c r="D71" s="2">
         <v>5.6623845100402832</v>
       </c>
       <c r="E71" s="2">
-        <v>5.6068077087402344</v>
+        <v>5.6060872077941895</v>
       </c>
     </row>
     <row r="72">
@@ -1253,13 +1253,13 @@
         <v>4.9118266105651855</v>
       </c>
       <c r="C72" s="2">
-        <v>4.7895646095275879</v>
+        <v>4.7912502288818359</v>
       </c>
       <c r="D72" s="2">
         <v>5.6130304336547852</v>
       </c>
       <c r="E72" s="2">
-        <v>5.5791335105895996</v>
+        <v>5.5781440734863281</v>
       </c>
     </row>
     <row r="73">
@@ -1270,13 +1270,13 @@
         <v>5.3106899261474609</v>
       </c>
       <c r="C73" s="2">
-        <v>5.2874870300292969</v>
+        <v>5.280583381652832</v>
       </c>
       <c r="D73" s="2">
         <v>5.6729302406311035</v>
       </c>
       <c r="E73" s="2">
-        <v>5.6190929412841797</v>
+        <v>5.6172547340393066</v>
       </c>
     </row>
     <row r="74">
@@ -1287,13 +1287,13 @@
         <v>6.3290963172912598</v>
       </c>
       <c r="C74" s="2">
-        <v>6.357184886932373</v>
+        <v>6.3434243202209473</v>
       </c>
       <c r="D74" s="2">
         <v>5.7780375480651855</v>
       </c>
       <c r="E74" s="2">
-        <v>5.7434682846069336</v>
+        <v>5.7410097122192383</v>
       </c>
     </row>
     <row r="75">
@@ -1304,13 +1304,13 @@
         <v>5.5417633056640625</v>
       </c>
       <c r="C75" s="2">
-        <v>5.7095522880554199</v>
+        <v>5.7031979560852051</v>
       </c>
       <c r="D75" s="2">
         <v>5.6354641914367676</v>
       </c>
       <c r="E75" s="2">
-        <v>5.6074094772338867</v>
+        <v>5.6051478385925293</v>
       </c>
     </row>
     <row r="76">
@@ -1321,13 +1321,13 @@
         <v>5.668339729309082</v>
       </c>
       <c r="C76" s="2">
-        <v>5.6833610534667969</v>
+        <v>5.6866903305053711</v>
       </c>
       <c r="D76" s="2">
         <v>5.698610782623291</v>
       </c>
       <c r="E76" s="2">
-        <v>5.6843938827514648</v>
+        <v>5.6820406913757324</v>
       </c>
     </row>
     <row r="77">
@@ -1338,13 +1338,13 @@
         <v>6.0549139976501465</v>
       </c>
       <c r="C77" s="2">
-        <v>5.878077507019043</v>
+        <v>5.8741397857666016</v>
       </c>
       <c r="D77" s="2">
         <v>5.7410635948181152</v>
       </c>
       <c r="E77" s="2">
-        <v>5.7328572273254395</v>
+        <v>5.7294259071350098</v>
       </c>
     </row>
     <row r="78">
@@ -1355,13 +1355,13 @@
         <v>5.9773707389831543</v>
       </c>
       <c r="C78" s="2">
-        <v>6.0176758766174316</v>
+        <v>6.0164003372192383</v>
       </c>
       <c r="D78" s="2">
         <v>5.7750325202941895</v>
       </c>
       <c r="E78" s="2">
-        <v>5.7481002807617188</v>
+        <v>5.7455306053161621</v>
       </c>
     </row>
     <row r="79">
@@ -1372,13 +1372,13 @@
         <v>5.4551982879638672</v>
       </c>
       <c r="C79" s="2">
-        <v>5.3512039184570312</v>
+        <v>5.3553986549377441</v>
       </c>
       <c r="D79" s="2">
         <v>5.8070149421691895</v>
       </c>
       <c r="E79" s="2">
-        <v>5.7726187705993652</v>
+        <v>5.7719922065734863</v>
       </c>
     </row>
     <row r="80">
@@ -1389,13 +1389,13 @@
         <v>6.0383000373840332</v>
       </c>
       <c r="C80" s="2">
-        <v>6.0854396820068359</v>
+        <v>6.0872802734375</v>
       </c>
       <c r="D80" s="2">
         <v>5.8738036155700684</v>
       </c>
       <c r="E80" s="2">
-        <v>5.7914280891418457</v>
+        <v>5.7911496162414551</v>
       </c>
     </row>
     <row r="81">
@@ -1406,13 +1406,13 @@
         <v>5.2938985824584961</v>
       </c>
       <c r="C81" s="2">
-        <v>5.2257328033447266</v>
+        <v>5.2177190780639648</v>
       </c>
       <c r="D81" s="2">
         <v>5.7924022674560547</v>
       </c>
       <c r="E81" s="2">
-        <v>5.7044878005981445</v>
+        <v>5.7044973373413086</v>
       </c>
     </row>
     <row r="82">
@@ -1423,13 +1423,13 @@
         <v>5.6164107322692871</v>
       </c>
       <c r="C82" s="2">
-        <v>5.4246745109558105</v>
+        <v>5.4255266189575195</v>
       </c>
       <c r="D82" s="2">
         <v>5.7079815864562988</v>
       </c>
       <c r="E82" s="2">
-        <v>5.6420331001281738</v>
+        <v>5.6423931121826172</v>
       </c>
     </row>
     <row r="83">
@@ -1440,13 +1440,13 @@
         <v>6.6169404983520508</v>
       </c>
       <c r="C83" s="2">
-        <v>6.5778522491455078</v>
+        <v>6.581578254699707</v>
       </c>
       <c r="D83" s="2">
         <v>5.6915946006774902</v>
       </c>
       <c r="E83" s="2">
-        <v>5.6135358810424805</v>
+        <v>5.6131148338317871</v>
       </c>
     </row>
     <row r="84">
@@ -1457,13 +1457,13 @@
         <v>6.1428580284118652</v>
       </c>
       <c r="C84" s="2">
-        <v>5.8788332939147949</v>
+        <v>5.8756113052368164</v>
       </c>
       <c r="D84" s="2">
         <v>5.6904311180114746</v>
       </c>
       <c r="E84" s="2">
-        <v>5.6071000099182129</v>
+        <v>5.6061296463012695</v>
       </c>
     </row>
     <row r="85">
@@ -1474,13 +1474,13 @@
         <v>4.93572998046875</v>
       </c>
       <c r="C85" s="2">
-        <v>4.9008994102478027</v>
+        <v>4.9068222045898438</v>
       </c>
       <c r="D85" s="2">
         <v>5.7829852104187012</v>
       </c>
       <c r="E85" s="2">
-        <v>5.6960062980651855</v>
+        <v>5.6949152946472168</v>
       </c>
     </row>
     <row r="86">
@@ -1491,13 +1491,13 @@
         <v>5.2951278686523438</v>
       </c>
       <c r="C86" s="2">
-        <v>5.3159856796264648</v>
+        <v>5.3152003288269043</v>
       </c>
       <c r="D86" s="2">
         <v>5.822411060333252</v>
       </c>
       <c r="E86" s="2">
-        <v>5.7405648231506348</v>
+        <v>5.7401480674743652</v>
       </c>
     </row>
     <row r="87">
@@ -1508,13 +1508,13 @@
         <v>5.8298854827880859</v>
       </c>
       <c r="C87" s="2">
-        <v>5.7612018585205078</v>
+        <v>5.7528958320617676</v>
       </c>
       <c r="D87" s="2">
         <v>5.9898324012756348</v>
       </c>
       <c r="E87" s="2">
-        <v>5.928290843963623</v>
+        <v>5.9277138710021973</v>
       </c>
     </row>
     <row r="88">
@@ -1525,13 +1525,13 @@
         <v>5.444730281829834</v>
       </c>
       <c r="C88" s="2">
-        <v>5.293278694152832</v>
+        <v>5.2925329208374023</v>
       </c>
       <c r="D88" s="2">
         <v>6.0257463455200195</v>
       </c>
       <c r="E88" s="2">
-        <v>5.9640440940856934</v>
+        <v>5.9632139205932617</v>
       </c>
     </row>
     <row r="89">
@@ -1542,13 +1542,13 @@
         <v>6.871284008026123</v>
       </c>
       <c r="C89" s="2">
-        <v>6.8855981826782227</v>
+        <v>6.8863496780395508</v>
       </c>
       <c r="D89" s="2">
         <v>6.0522208213806152</v>
       </c>
       <c r="E89" s="2">
-        <v>6.0079507827758789</v>
+        <v>6.0070652961730957</v>
       </c>
     </row>
     <row r="90">
@@ -1559,13 +1559,13 @@
         <v>5.6487321853637695</v>
       </c>
       <c r="C90" s="2">
-        <v>5.6267585754394531</v>
+        <v>5.62481689453125</v>
       </c>
       <c r="D90" s="2">
         <v>6.0533194541931152</v>
       </c>
       <c r="E90" s="2">
-        <v>6.0130624771118164</v>
+        <v>6.0125164985656738</v>
       </c>
     </row>
     <row r="91">
@@ -1576,13 +1576,13 @@
         <v>7.1232032775878906</v>
       </c>
       <c r="C91" s="2">
-        <v>7.1142115592956543</v>
+        <v>7.113619327545166</v>
       </c>
       <c r="D91" s="2">
         <v>6.1775832176208496</v>
       </c>
       <c r="E91" s="2">
-        <v>6.1433825492858887</v>
+        <v>6.142366886138916</v>
       </c>
     </row>
     <row r="92">
@@ -1593,13 +1593,13 @@
         <v>6.9401650428771973</v>
       </c>
       <c r="C92" s="2">
-        <v>6.899630069732666</v>
+        <v>6.9010787010192871</v>
       </c>
       <c r="D92" s="2">
         <v>6.179023265838623</v>
       </c>
       <c r="E92" s="2">
-        <v>6.1603803634643555</v>
+        <v>6.1607761383056641</v>
       </c>
     </row>
     <row r="93">
@@ -1610,13 +1610,13 @@
         <v>6.3811273574829102</v>
       </c>
       <c r="C93" s="2">
-        <v>6.2739911079406738</v>
+        <v>6.2702698707580566</v>
       </c>
       <c r="D93" s="2">
         <v>6.2834682464599609</v>
       </c>
       <c r="E93" s="2">
-        <v>6.2642951011657715</v>
+        <v>6.2653341293334961</v>
       </c>
     </row>
     <row r="94">
@@ -1627,13 +1627,13 @@
         <v>4.9456191062927246</v>
       </c>
       <c r="C94" s="2">
-        <v>4.9469070434570312</v>
+        <v>4.9558835029602051</v>
       </c>
       <c r="D94" s="2">
         <v>6.2054262161254883</v>
       </c>
       <c r="E94" s="2">
-        <v>6.1558361053466797</v>
+        <v>6.1566791534423828</v>
       </c>
     </row>
     <row r="95">
@@ -1644,13 +1644,13 @@
         <v>6.4135041236877441</v>
       </c>
       <c r="C95" s="2">
-        <v>6.4888668060302734</v>
+        <v>6.483856201171875</v>
       </c>
       <c r="D95" s="2">
         <v>6.1821441650390625</v>
       </c>
       <c r="E95" s="2">
-        <v>6.1391654014587402</v>
+        <v>6.1402420997619629</v>
       </c>
     </row>
     <row r="96">
@@ -1661,13 +1661,13 @@
         <v>5.8428459167480469</v>
       </c>
       <c r="C96" s="2">
-        <v>5.9141802787780762</v>
+        <v>5.918576717376709</v>
       </c>
       <c r="D96" s="2">
         <v>6.131619930267334</v>
       </c>
       <c r="E96" s="2">
-        <v>6.0939216613769531</v>
+        <v>6.0953483581542969</v>
       </c>
     </row>
     <row r="97">
@@ -1678,13 +1678,13 @@
         <v>6.3847346305847168</v>
       </c>
       <c r="C97" s="2">
-        <v>6.2285141944885254</v>
+        <v>6.2335567474365234</v>
       </c>
       <c r="D97" s="2">
         <v>6.0031008720397949</v>
       </c>
       <c r="E97" s="2">
-        <v>5.9607758522033691</v>
+        <v>5.9621195793151855</v>
       </c>
     </row>
     <row r="98">
@@ -1695,13 +1695,13 @@
         <v>6.1689062118530273</v>
       </c>
       <c r="C98" s="2">
-        <v>5.9094653129577637</v>
+        <v>5.9084563255310059</v>
       </c>
       <c r="D98" s="2">
         <v>5.9465999603271484</v>
       </c>
       <c r="E98" s="2">
-        <v>5.90411376953125</v>
+        <v>5.9049654006958008</v>
       </c>
     </row>
     <row r="99">
@@ -1712,13 +1712,13 @@
         <v>5.4391937255859375</v>
       </c>
       <c r="C99" s="2">
-        <v>5.4767217636108398</v>
+        <v>5.4768805503845215</v>
       </c>
       <c r="D99" s="2">
         <v>6.055762767791748</v>
       </c>
       <c r="E99" s="2">
-        <v>6.0129880905151367</v>
+        <v>6.0132560729980469</v>
       </c>
     </row>
     <row r="100">
@@ -1729,13 +1729,13 @@
         <v>6.6684823036193848</v>
       </c>
       <c r="C100" s="2">
-        <v>6.7070164680480957</v>
+        <v>6.7095756530761719</v>
       </c>
       <c r="D100" s="2">
         <v>6.0038275718688965</v>
       </c>
       <c r="E100" s="2">
-        <v>5.9423069953918457</v>
+        <v>5.9436473846435547</v>
       </c>
     </row>
     <row r="101">
@@ -1746,13 +1746,13 @@
         <v>5.7834963798522949</v>
       </c>
       <c r="C101" s="2">
-        <v>5.7013177871704102</v>
+        <v>5.702021598815918</v>
       </c>
       <c r="D101" s="2">
         <v>6.0322632789611816</v>
       </c>
       <c r="E101" s="2">
-        <v>5.9715290069580078</v>
+        <v>5.9717578887939453</v>
       </c>
     </row>
     <row r="102">
@@ -1763,13 +1763,13 @@
         <v>5.8726191520690918</v>
       </c>
       <c r="C102" s="2">
-        <v>5.7640361785888672</v>
+        <v>5.7558813095092773</v>
       </c>
       <c r="D102" s="2">
         <v>5.9267077445983887</v>
       </c>
       <c r="E102" s="2">
-        <v>5.8702044486999512</v>
+        <v>5.870297908782959</v>
       </c>
     </row>
     <row r="103">
@@ -1780,13 +1780,13 @@
         <v>5.9280815124511719</v>
       </c>
       <c r="C103" s="2">
-        <v>5.9267754554748535</v>
+        <v>5.9304981231689453</v>
       </c>
       <c r="D103" s="2">
         <v>5.9088234901428223</v>
       </c>
       <c r="E103" s="2">
-        <v>5.8756704330444336</v>
+        <v>5.8753652572631836</v>
       </c>
     </row>
     <row r="104">
@@ -1797,13 +1797,13 @@
         <v>5.9460883140563965</v>
       </c>
       <c r="C104" s="2">
-        <v>5.8527336120605469</v>
+        <v>5.8573794364929199</v>
       </c>
       <c r="D104" s="2">
         <v>6.0314702987670898</v>
       </c>
       <c r="E104" s="2">
-        <v>5.983281135559082</v>
+        <v>5.9841976165771484</v>
       </c>
     </row>
     <row r="105">
@@ -1814,13 +1814,13 @@
         <v>6.0987663269042969</v>
       </c>
       <c r="C105" s="2">
-        <v>6.1771793365478516</v>
+        <v>6.1715707778930664</v>
       </c>
       <c r="D105" s="2">
         <v>6.0353260040283203</v>
       </c>
       <c r="E105" s="2">
-        <v>5.9766225814819336</v>
+        <v>5.9779577255249023</v>
       </c>
     </row>
     <row r="106">
@@ -1831,13 +1831,13 @@
         <v>5.4347352981567383</v>
       </c>
       <c r="C106" s="2">
-        <v>5.3165922164916992</v>
+        <v>5.3204159736633301</v>
       </c>
       <c r="D106" s="2">
         <v>6.2126164436340332</v>
       </c>
       <c r="E106" s="2">
-        <v>6.1356234550476074</v>
+        <v>6.1373076438903809</v>
       </c>
     </row>
     <row r="107">
@@ -1848,13 +1848,13 @@
         <v>6.0079493522644043</v>
       </c>
       <c r="C107" s="2">
-        <v>5.9586601257324219</v>
+        <v>5.9540619850158691</v>
       </c>
       <c r="D107" s="2">
         <v>6.3129463195800781</v>
       </c>
       <c r="E107" s="2">
-        <v>6.2491755485534668</v>
+        <v>6.2512984275817871</v>
       </c>
     </row>
     <row r="108">
@@ -1865,13 +1865,13 @@
         <v>6.5430121421813965</v>
       </c>
       <c r="C108" s="2">
-        <v>6.4452195167541504</v>
+        <v>6.4563727378845215</v>
       </c>
       <c r="D108" s="2">
         <v>6.4722661972045898</v>
       </c>
       <c r="E108" s="2">
-        <v>6.3943452835083008</v>
+        <v>6.3957381248474121</v>
       </c>
     </row>
     <row r="109">
@@ -1882,13 +1882,13 @@
         <v>6.7031855583190918</v>
       </c>
       <c r="C109" s="2">
-        <v>6.6470880508422852</v>
+        <v>6.653416633605957</v>
       </c>
       <c r="D109" s="2">
         <v>6.6922817230224609</v>
       </c>
       <c r="E109" s="2">
-        <v>6.6405415534973145</v>
+        <v>6.640045166015625</v>
       </c>
     </row>
     <row r="110">
@@ -1899,13 +1899,13 @@
         <v>7.3791117668151855</v>
       </c>
       <c r="C110" s="2">
-        <v>7.1323261260986328</v>
+        <v>7.1361737251281738</v>
       </c>
       <c r="D110" s="2">
         <v>6.9277563095092773</v>
       </c>
       <c r="E110" s="2">
-        <v>6.858428955078125</v>
+        <v>6.8582096099853516</v>
       </c>
     </row>
     <row r="111">
@@ -1916,13 +1916,13 @@
         <v>6.7755856513977051</v>
       </c>
       <c r="C111" s="2">
-        <v>6.7860074043273926</v>
+        <v>6.781794548034668</v>
       </c>
       <c r="D111" s="2">
         <v>7.1573972702026367</v>
       </c>
       <c r="E111" s="2">
-        <v>7.078284740447998</v>
+        <v>7.0776872634887695</v>
       </c>
     </row>
     <row r="112">
@@ -1933,13 +1933,13 @@
         <v>7.3619632720947266</v>
       </c>
       <c r="C112" s="2">
-        <v>7.2333011627197266</v>
+        <v>7.2304582595825195</v>
       </c>
       <c r="D112" s="2">
         <v>7.2840347290039062</v>
       </c>
       <c r="E112" s="2">
-        <v>7.2168540954589844</v>
+        <v>7.2160768508911133</v>
       </c>
     </row>
     <row r="113">
@@ -1950,13 +1950,13 @@
         <v>7.9262242317199707</v>
       </c>
       <c r="C113" s="2">
-        <v>8.0684986114501953</v>
+        <v>8.0561408996582031</v>
       </c>
       <c r="D113" s="2">
         <v>7.3420815467834473</v>
       </c>
       <c r="E113" s="2">
-        <v>7.2800612449645996</v>
+        <v>7.2777161598205566</v>
       </c>
     </row>
     <row r="114">
@@ -1967,13 +1967,13 @@
         <v>8.2180414199829102</v>
       </c>
       <c r="C114" s="2">
-        <v>8.1381664276123047</v>
+        <v>8.1350526809692383</v>
       </c>
       <c r="D114" s="2">
         <v>7.3419795036315918</v>
       </c>
       <c r="E114" s="2">
-        <v>7.2581310272216797</v>
+        <v>7.255040168762207</v>
       </c>
     </row>
     <row r="115">
@@ -1984,13 +1984,13 @@
         <v>7.5015029907226562</v>
       </c>
       <c r="C115" s="2">
-        <v>7.2952933311462402</v>
+        <v>7.2957158088684082</v>
       </c>
       <c r="D115" s="2">
         <v>7.3138532638549805</v>
       </c>
       <c r="E115" s="2">
-        <v>7.2677741050720215</v>
+        <v>7.2635278701782227</v>
       </c>
     </row>
     <row r="116">
@@ -2001,13 +2001,13 @@
         <v>7.1476860046386719</v>
       </c>
       <c r="C116" s="2">
-        <v>7.205787181854248</v>
+        <v>7.1995654106140137</v>
       </c>
       <c r="D116" s="2">
         <v>7.4304714202880859</v>
       </c>
       <c r="E116" s="2">
-        <v>7.3884553909301758</v>
+        <v>7.3844842910766602</v>
       </c>
     </row>
     <row r="117">
@@ -2018,13 +2018,13 @@
         <v>7.0654339790344238</v>
       </c>
       <c r="C117" s="2">
-        <v>7.0140833854675293</v>
+        <v>7.0111289024353027</v>
       </c>
       <c r="D117" s="2">
         <v>7.4479308128356934</v>
       </c>
       <c r="E117" s="2">
-        <v>7.4199295043945312</v>
+        <v>7.4148144721984863</v>
       </c>
     </row>
     <row r="118">
@@ -2035,13 +2035,13 @@
         <v>6.7022643089294434</v>
       </c>
       <c r="C118" s="2">
-        <v>6.4497160911560059</v>
+        <v>6.4493312835693359</v>
       </c>
       <c r="D118" s="2">
         <v>7.5023574829101562</v>
       </c>
       <c r="E118" s="2">
-        <v>7.4489741325378418</v>
+        <v>7.4452910423278809</v>
       </c>
     </row>
     <row r="119">
@@ -2052,13 +2052,13 @@
         <v>7.1259779930114746</v>
       </c>
       <c r="C119" s="2">
-        <v>7.2191123962402344</v>
+        <v>7.2125611305236816</v>
       </c>
       <c r="D119" s="2">
         <v>7.454254150390625</v>
       </c>
       <c r="E119" s="2">
-        <v>7.4104900360107422</v>
+        <v>7.4061532020568848</v>
       </c>
     </row>
     <row r="120">
@@ -2069,13 +2069,13 @@
         <v>7.8251481056213379</v>
       </c>
       <c r="C120" s="2">
-        <v>7.8721408843994141</v>
+        <v>7.8704061508178711</v>
       </c>
       <c r="D120" s="2">
         <v>7.4977941513061523</v>
       </c>
       <c r="E120" s="2">
-        <v>7.4688215255737305</v>
+        <v>7.4636740684509277</v>
       </c>
     </row>
     <row r="121">
@@ -2086,13 +2086,13 @@
         <v>7.5191001892089844</v>
       </c>
       <c r="C121" s="2">
-        <v>7.5165657997131348</v>
+        <v>7.5034270286560059</v>
       </c>
       <c r="D121" s="2">
         <v>7.5405926704406738</v>
       </c>
       <c r="E121" s="2">
-        <v>7.4883313179016113</v>
+        <v>7.4843707084655762</v>
       </c>
     </row>
     <row r="122">
@@ -2103,13 +2103,13 @@
         <v>8.4160623550415039</v>
       </c>
       <c r="C122" s="2">
-        <v>8.3299026489257812</v>
+        <v>8.3304300308227539</v>
       </c>
       <c r="D122" s="2">
         <v>7.5500564575195312</v>
       </c>
       <c r="E122" s="2">
-        <v>7.4810442924499512</v>
+        <v>7.478306770324707</v>
       </c>
     </row>
     <row r="123">
@@ -2120,13 +2120,13 @@
         <v>7.7851109504699707</v>
       </c>
       <c r="C123" s="2">
-        <v>7.7918095588684082</v>
+        <v>7.782813549041748</v>
       </c>
       <c r="D123" s="2">
         <v>7.5490827560424805</v>
       </c>
       <c r="E123" s="2">
-        <v>7.4972519874572754</v>
+        <v>7.4944286346435547</v>
       </c>
     </row>
     <row r="124">
@@ -2137,13 +2137,13 @@
         <v>7.8933625221252441</v>
       </c>
       <c r="C124" s="2">
-        <v>7.8202738761901855</v>
+        <v>7.8134036064147949</v>
       </c>
       <c r="D124" s="2">
         <v>7.5225167274475098</v>
       </c>
       <c r="E124" s="2">
-        <v>7.4814629554748535</v>
+        <v>7.4791135787963867</v>
       </c>
     </row>
     <row r="125">
@@ -2154,13 +2154,13 @@
         <v>7.532874584197998</v>
       </c>
       <c r="C125" s="2">
-        <v>7.3813762664794922</v>
+        <v>7.3858327865600586</v>
       </c>
       <c r="D125" s="2">
         <v>7.3106889724731445</v>
       </c>
       <c r="E125" s="2">
-        <v>7.2616367340087891</v>
+        <v>7.2589154243469238</v>
       </c>
     </row>
     <row r="126">
@@ -2171,13 +2171,13 @@
         <v>7.1506085395812988</v>
       </c>
       <c r="C126" s="2">
-        <v>6.9485001564025879</v>
+        <v>6.9565539360046387</v>
       </c>
       <c r="D126" s="2">
         <v>7.2155447006225586</v>
       </c>
       <c r="E126" s="2">
-        <v>7.1496925354003906</v>
+        <v>7.1483564376831055</v>
       </c>
     </row>
     <row r="127">
@@ -2188,13 +2188,13 @@
         <v>6.6934981346130371</v>
       </c>
       <c r="C127" s="2">
-        <v>6.5955867767333984</v>
+        <v>6.5944314002990723</v>
       </c>
       <c r="D127" s="2">
         <v>7.0192604064941406</v>
       </c>
       <c r="E127" s="2">
-        <v>6.953916072845459</v>
+        <v>6.9528827667236328</v>
       </c>
     </row>
     <row r="128">
@@ -2205,13 +2205,13 @@
         <v>6.8868856430053711</v>
       </c>
       <c r="C128" s="2">
-        <v>7.0770106315612793</v>
+        <v>7.0747222900390625</v>
       </c>
       <c r="D128" s="2">
         <v>6.9047675132751465</v>
       </c>
       <c r="E128" s="2">
-        <v>6.8599748611450195</v>
+        <v>6.8608736991882324</v>
       </c>
     </row>
     <row r="129">
@@ -2222,13 +2222,13 @@
         <v>5.9186968803405762</v>
       </c>
       <c r="C129" s="2">
-        <v>5.893704891204834</v>
+        <v>5.8886232376098633</v>
       </c>
       <c r="D129" s="2">
         <v>6.7313752174377441</v>
       </c>
       <c r="E129" s="2">
-        <v>6.6899433135986328</v>
+        <v>6.6918964385986328</v>
       </c>
     </row>
     <row r="130">
@@ -2239,13 +2239,13 @@
         <v>6.6628012657165527</v>
       </c>
       <c r="C130" s="2">
-        <v>6.5090689659118652</v>
+        <v>6.5083980560302734</v>
       </c>
       <c r="D130" s="2">
         <v>6.7171320915222168</v>
       </c>
       <c r="E130" s="2">
-        <v>6.6849656105041504</v>
+        <v>6.6859321594238281</v>
       </c>
     </row>
     <row r="131">
@@ -2256,13 +2256,13 @@
         <v>6.649505615234375</v>
       </c>
       <c r="C131" s="2">
-        <v>6.5679135322570801</v>
+        <v>6.5711655616760254</v>
       </c>
       <c r="D131" s="2">
         <v>6.6962227821350098</v>
       </c>
       <c r="E131" s="2">
-        <v>6.6993699073791504</v>
+        <v>6.6990604400634766</v>
       </c>
     </row>
     <row r="132">
@@ -2273,13 +2273,13 @@
         <v>6.7546758651733398</v>
       </c>
       <c r="C132" s="2">
-        <v>6.9463405609130859</v>
+        <v>6.9547338485717773</v>
       </c>
       <c r="D132" s="2">
         <v>6.7168769836425781</v>
       </c>
       <c r="E132" s="2">
-        <v>6.7345385551452637</v>
+        <v>6.734011173248291</v>
       </c>
     </row>
     <row r="133">
@@ -2290,13 +2290,13 @@
         <v>6.3328285217285156</v>
       </c>
       <c r="C133" s="2">
-        <v>6.2899875640869141</v>
+        <v>6.2926082611083984</v>
       </c>
       <c r="D133" s="2">
         <v>6.6695919036865234</v>
       </c>
       <c r="E133" s="2">
-        <v>6.6449704170227051</v>
+        <v>6.6446933746337891</v>
       </c>
     </row>
     <row r="134">
@@ -2307,13 +2307,13 @@
         <v>7.4046893119812012</v>
       </c>
       <c r="C134" s="2">
-        <v>7.3365778923034668</v>
+        <v>7.3321514129638672</v>
       </c>
       <c r="D134" s="2">
         <v>6.7932062149047852</v>
       </c>
       <c r="E134" s="2">
-        <v>6.7672710418701172</v>
+        <v>6.7682938575744629</v>
       </c>
     </row>
     <row r="135">
@@ -2324,13 +2324,13 @@
         <v>6.9624247550964355</v>
       </c>
       <c r="C135" s="2">
-        <v>7.0781373977661133</v>
+        <v>7.0747108459472656</v>
       </c>
       <c r="D135" s="2">
         <v>6.7545914649963379</v>
       </c>
       <c r="E135" s="2">
-        <v>6.7322287559509277</v>
+        <v>6.7328939437866211</v>
       </c>
     </row>
     <row r="136">
@@ -2341,13 +2341,13 @@
         <v>6.8793830871582031</v>
       </c>
       <c r="C136" s="2">
-        <v>6.9121060371398926</v>
+        <v>6.9089870452880859</v>
       </c>
       <c r="D136" s="2">
         <v>6.7116742134094238</v>
       </c>
       <c r="E136" s="2">
-        <v>6.6964583396911621</v>
+        <v>6.6955647468566895</v>
       </c>
     </row>
     <row r="137">
@@ -2358,13 +2358,13 @@
         <v>6.4613208770751953</v>
       </c>
       <c r="C137" s="2">
-        <v>6.2708978652954102</v>
+        <v>6.2708621025085449</v>
       </c>
       <c r="D137" s="2">
-        <v>6.706298828125</v>
+        <v>6.8301424980163574</v>
       </c>
       <c r="E137" s="2">
-        <v>6.6652231216430664</v>
+        <v>6.8097267150878906</v>
       </c>
     </row>
     <row r="138">
@@ -2375,13 +2375,13 @@
         <v>7.0312271118164062</v>
       </c>
       <c r="C138" s="2">
-        <v>6.9944100379943848</v>
+        <v>7.0010290145874023</v>
       </c>
       <c r="D138" s="2">
-        <v>6.7596521377563477</v>
+        <v>6.9436264038085938</v>
       </c>
       <c r="E138" s="2">
-        <v>6.7188282012939453</v>
+        <v>6.8967165946960449</v>
       </c>
     </row>
     <row r="139">
@@ -2392,13 +2392,13 @@
         <v>6.3152675628662109</v>
       </c>
       <c r="C139" s="2">
-        <v>6.1936869621276855</v>
+        <v>6.1897974014282227</v>
       </c>
       <c r="D139" s="2">
-        <v>6.6521458625793457</v>
+        <v>6.7496628761291504</v>
       </c>
       <c r="E139" s="2">
-        <v>6.6158695220947266</v>
+        <v>6.7153277397155762</v>
       </c>
     </row>
     <row r="140">
@@ -2409,95 +2409,239 @@
         <v>6.2632513046264648</v>
       </c>
       <c r="C140" s="2">
-        <v>6.2459797859191895</v>
+        <v>6.2352032661437988</v>
       </c>
       <c r="D140" s="2">
-        <v>6.5900897979736328</v>
+        <v>6.7621073722839355</v>
       </c>
       <c r="E140" s="2">
-        <v>6.5234160423278809</v>
+        <v>6.7135782241821289</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1">
         <v>45505</v>
       </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
+      <c r="B141" s="2">
+        <v>7.8208909034729004</v>
+      </c>
+      <c r="C141" s="2">
+        <v>7.9821915626525879</v>
+      </c>
+      <c r="D141" s="2">
+        <v>6.8722906112670898</v>
+      </c>
+      <c r="E141" s="2">
+        <v>6.8068618774414062</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1">
         <v>45536</v>
       </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
+      <c r="B142" s="2">
+        <v>7.3541808128356934</v>
+      </c>
+      <c r="C142" s="2">
+        <v>7.0755167007446289</v>
+      </c>
+      <c r="D142" s="2">
+        <v>7.0514559745788574</v>
+      </c>
+      <c r="E142" s="2">
+        <v>6.9992127418518066</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1">
         <v>45566</v>
       </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
+      <c r="B143" s="2">
+        <v>5.6590175628662109</v>
+      </c>
+      <c r="C143" s="2">
+        <v>5.699653148651123</v>
+      </c>
+      <c r="D143" s="2">
+        <v>7.1896300315856934</v>
+      </c>
+      <c r="E143" s="2">
+        <v>7.1575369834899902</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1">
         <v>45597</v>
       </c>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
+      <c r="B144" s="2">
+        <v>7.0744271278381348</v>
+      </c>
+      <c r="C144" s="2">
+        <v>7.0589628219604492</v>
+      </c>
+      <c r="D144" s="2">
+        <v>7.3382205963134766</v>
+      </c>
+      <c r="E144" s="2">
+        <v>7.3154535293579102</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1">
         <v>45627</v>
       </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="B145" s="2">
+        <v>7.871030330657959</v>
+      </c>
+      <c r="C145" s="2">
+        <v>7.7485427856445312</v>
+      </c>
+      <c r="D145" s="2">
+        <v>7.3620023727416992</v>
+      </c>
+      <c r="E145" s="2">
+        <v>7.3538775444030762</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1">
         <v>45658</v>
       </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
+      <c r="B146" s="2">
+        <v>8.0738124847412109</v>
+      </c>
+      <c r="C146" s="2">
+        <v>8.0020198822021484</v>
+      </c>
+      <c r="D146" s="2">
+        <v>7.3046412467956543</v>
+      </c>
+      <c r="E146" s="2">
+        <v>7.2753381729125977</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1">
         <v>45689</v>
       </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="B147" s="2">
+        <v>8.2747907638549805</v>
+      </c>
+      <c r="C147" s="2">
+        <v>8.4259443283081055</v>
+      </c>
+      <c r="D147" s="2">
+        <v>7.2975640296936035</v>
+      </c>
+      <c r="E147" s="2">
+        <v>7.3038845062255859</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1">
         <v>45717</v>
       </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
+      <c r="B148" s="2">
+        <v>7.6525821685791016</v>
+      </c>
+      <c r="C148" s="2">
+        <v>7.6110472679138184</v>
+      </c>
+      <c r="D148" s="2">
+        <v>7.5706548690795898</v>
+      </c>
+      <c r="E148" s="2">
+        <v>7.571256160736084</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1">
         <v>45748</v>
       </c>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
+      <c r="B149" s="2">
+        <v>6.477287769317627</v>
+      </c>
+      <c r="C149" s="2">
+        <v>6.5810203552246094</v>
+      </c>
+      <c r="D149" s="2">
+        <v>7.6699008941650391</v>
+      </c>
+      <c r="E149" s="2">
+        <v>7.6737151145935059</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
     </row>
   </sheetData>
 </worksheet>
